--- a/results/final_20260514_v2_summary/scene_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/scene_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.1170±0.0101</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0884±0.0125</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0561±0.0152</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.0873±0.0283</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9484±0.0025</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9573±0.0049</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.9621±0.0045</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.9533±0.0062</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.8420±0.0104</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.8524±0.0189</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.8419±0.0189</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.7519±0.0300</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.8287±0.0117</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.8489±0.0178</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.8611±0.0167</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.8229±0.0241</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.8303±0.0109</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.8448±0.0181</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.8433±0.0177</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.7721±0.0265</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9330±0.0036</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.9379±0.0067</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.9317±0.0083</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.8779±0.0144</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.8203±0.0110</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.8331±0.0182</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.8272±0.0188</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7437±0.0291</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.8388±0.0099</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.8556±0.0154</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.8570±0.0159</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.7920±0.0215</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.8396±0.0116</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.8417±0.0188</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.8139±0.0207</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.6992±0.0293</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.8426±0.0103</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.8746±0.0144</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.9088±0.0137</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.9277±0.0154</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.2868±0.0575</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.2498±0.0407</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.1600±0.0584</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.1710±0.0543</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.8355±0.0092</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.8556±0.0151</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.8602±0.0164</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.8023±0.0216</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.8364±0.0126</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.8406±0.0189</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.8144±0.0218</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.7027±0.0316</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.8346±0.0075</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.8712±0.0146</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.9116±0.0130</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.9359±0.0136</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.8089±0.0085</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.8258±0.0185</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.8267±0.0188</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.7717±0.0303</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.7903±0.0110</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.7979±0.0194</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.7798±0.0235</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.6614±0.0401</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.1006±0.0086</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.0753±0.0122</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0515±0.0153</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.0961±0.0256</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9474±0.0025</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9558±0.0049</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.9601±0.0045</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.9506±0.0066</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.8386±0.0124</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.8467±0.0189</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.8346±0.0190</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7425±0.0308</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8414±0.0121</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8576±0.0163</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8644±0.0164</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.8252±0.0241</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.8327±0.0116</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.8442±0.0173</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.8397±0.0175</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.7664±0.0268</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9318±0.0033</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.9357±0.0066</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.9282±0.0081</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.8710±0.0149</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.8181±0.0113</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.8283±0.0177</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.8207±0.0185</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7346±0.0299</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.8394±0.0094</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.8535±0.0145</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.8518±0.0150</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.7836±0.0228</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.8276±0.0135</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.8288±0.0197</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.8016±0.0200</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6852±0.0303</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.8550±0.0086</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.8838±0.0128</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.9129±0.0130</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.9304±0.0146</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.2501±0.0491</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.2113±0.0450</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.1401±0.0526</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.1815±0.0543</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.8351±0.0087</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.8526±0.0144</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.8546±0.0157</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7937±0.0223</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.8229±0.0136</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.8265±0.0196</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.8013±0.0211</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6883±0.0322</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.8478±0.0053</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.8807±0.0132</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.9156±0.0121</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.9383±0.0127</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.7944±0.0095</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.8111±0.0200</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.8148±0.0192</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.7592±0.0321</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.7744±0.0113</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.7810±0.0207</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.7648±0.0233</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6429±0.0423</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.1195±0.0094</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.0895±0.0125</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0566±0.0147</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.0867±0.0284</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9478±0.0023</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9572±0.0047</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.9620±0.0045</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.9531±0.0062</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.8402±0.0091</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.8521±0.0183</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.8417±0.0189</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.7509±0.0299</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.8258±0.0097</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.8478±0.0172</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.8602±0.0165</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.8222±0.0242</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.8281±0.0093</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.8443±0.0175</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.8428±0.0176</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.7712±0.0264</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9322±0.0030</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.9378±0.0064</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.9316±0.0082</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.8773±0.0144</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.8183±0.0096</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.8328±0.0176</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.8269±0.0187</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.7428±0.0290</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.8369±0.0082</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.8552±0.0148</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.8565±0.0156</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.7911±0.0216</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.8386±0.0105</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.8420±0.0181</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.8139±0.0205</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.6983±0.0292</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.8399±0.0090</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.8736±0.0140</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.9077±0.0131</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.9268±0.0158</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.2942±0.0469</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.2534±0.0414</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.1626±0.0595</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.1713±0.0540</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.8333±0.0078</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.8552±0.0145</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.8598±0.0162</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.8014±0.0216</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.8352±0.0117</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.8410±0.0182</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.8144±0.0217</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.7018±0.0315</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.8315±0.0060</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.8701±0.0142</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.9106±0.0127</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.9350±0.0141</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.8076±0.0086</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.8263±0.0178</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.8268±0.0186</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.7708±0.0303</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.7890±0.0106</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.7985±0.0187</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.7800±0.0233</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.6602±0.0401</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.1018±0.0081</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0756±0.0120</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0515±0.0150</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.0962±0.0254</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9469±0.0029</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9557±0.0048</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.9601±0.0046</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.9503±0.0066</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.8368±0.0131</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.8465±0.0185</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.8345±0.0191</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.7414±0.0306</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8396±0.0124</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.8574±0.0159</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.8644±0.0164</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.8246±0.0240</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.8309±0.0122</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.8440±0.0169</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.8397±0.0176</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.7654±0.0267</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9311±0.0036</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.9357±0.0064</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.9282±0.0082</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.8703±0.0150</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.8163±0.0120</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.8281±0.0174</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.8206±0.0187</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.7335±0.0298</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.8378±0.0099</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.8534±0.0141</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.8518±0.0151</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.7827±0.0229</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.8260±0.0144</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.8287±0.0193</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.8015±0.0202</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.6842±0.0303</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.8534±0.0081</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.8837±0.0124</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.9129±0.0130</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.9298±0.0147</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.2541±0.0522</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.2119±0.0442</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.1405±0.0531</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.1821±0.0535</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.8334±0.0095</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.8525±0.0139</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.8545±0.0159</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.7927±0.0224</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.8212±0.0145</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.8264±0.0192</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.8012±0.0214</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.6871±0.0322</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.8460±0.0053</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.8806±0.0129</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.9156±0.0122</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.9377±0.0130</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.7927±0.0107</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.8110±0.0198</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.8147±0.0195</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.7581±0.0319</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.7726±0.0121</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.7808±0.0204</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.7647±0.0236</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.6413±0.0422</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.1237±0.0133</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.1116±0.0122</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0911±0.0139</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.0572±0.0165</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9462±0.0030</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9448±0.0049</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.9338±0.0057</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.8896±0.0084</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.8384±0.0100</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.8336±0.0171</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.7994±0.0175</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.6935±0.0218</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.8201±0.0129</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.8252±0.0169</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.8184±0.0178</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.8135±0.0174</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.8241±0.0112</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.8227±0.0164</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.7982±0.0171</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.7266±0.0179</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9313±0.0042</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.9293±0.0063</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.9151±0.0071</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.8630±0.0091</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.8138±0.0114</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.8091±0.0162</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.7771±0.0171</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.6761±0.0197</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.8343±0.0106</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.8319±0.0142</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.8087±0.0157</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.7251±0.0145</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.8375±0.0090</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.8248±0.0161</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.7762±0.0167</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.6354±0.0189</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.8365±0.0133</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.8442±0.0155</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.8491±0.0174</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.8525±0.0115</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.3105±0.0602</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.2922±0.0424</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.2493±0.0583</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.1375±0.0596</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.8304±0.0102</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.8278±0.0149</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.8023±0.0160</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.7153±0.0161</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.8335±0.0109</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.8212±0.0171</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.7671±0.0176</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.6197±0.0215</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.8274±0.0113</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.8346±0.0148</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.8410±0.0172</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.8462±0.0116</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.7993±0.0107</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.7855±0.0155</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.7304±0.0186</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.5404±0.0301</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.7832±0.0122</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.7686±0.0166</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.7148±0.0188</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.5299±0.0284</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.1002±0.0090</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0815±0.0116</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0531±0.0133</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0897±0.0197</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9436±0.0034</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9407±0.0043</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.9222±0.0052</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.8541±0.0108</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.8290±0.0123</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.8188±0.0154</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.7634±0.0151</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.6082±0.0226</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.8348±0.0127</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.8449±0.0135</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.8431±0.0136</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.8435±0.0176</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.8239±0.0118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.8207±0.0134</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.7842±0.0134</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.6785±0.0165</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9282±0.0045</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.9244±0.0051</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.9008±0.0060</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.8202±0.0109</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.8078±0.0116</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.7981±0.0134</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.7468±0.0144</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.5969±0.0212</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.8323±0.0111</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.8279±0.0108</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.7906±0.0124</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.6760±0.0142</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.8172±0.0132</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.7972±0.0151</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.7254±0.0169</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.5522±0.0188</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.8518±0.0109</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.8654±0.0121</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.8741±0.0141</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.8832±0.0116</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.2544±0.0710</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.2199±0.0478</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.1455±0.0481</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.1717±0.0426</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.8268±0.0106</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.8220±0.0115</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.7819±0.0124</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.6649±0.0151</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.8102±0.0141</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.7895±0.0159</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.7116±0.0160</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.5352±0.0190</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.8442±0.0087</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.8575±0.0113</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.8679±0.0142</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.8785±0.0121</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.7773±0.0099</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.7495±0.0167</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.6560±0.0200</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.3811±0.0412</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.7598±0.0111</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.7307±0.0164</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.6371±0.0202</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.3679±0.0384</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.1277±0.0100</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.1167±0.0119</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0955±0.0142</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.0595±0.0157</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9459±0.0030</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9443±0.0050</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.9348±0.0052</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.8910±0.0084</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.8390±0.0111</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.8329±0.0178</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.8027±0.0169</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.6980±0.0230</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.8172±0.0118</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.8206±0.0169</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.8158±0.0176</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.8090±0.0172</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.8230±0.0113</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.8204±0.0170</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.7993±0.0169</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.7280±0.0188</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9310±0.0042</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.9286±0.0066</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.9162±0.0067</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.8646±0.0094</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.8129±0.0117</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.8077±0.0169</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.7795±0.0168</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.6799±0.0210</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.8327±0.0109</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.8299±0.0149</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.8100±0.0149</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.7261±0.0153</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.8386±0.0108</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.8259±0.0172</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.7815±0.0154</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.6399±0.0204</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.8323±0.0116</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.8393±0.0154</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.8457±0.0170</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.8468±0.0115</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.3256±0.0499</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.3057±0.0432</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.2558±0.0572</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.1466±0.0613</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.8290±0.0101</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.8258±0.0154</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.8039±0.0150</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.7167±0.0167</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.8351±0.0127</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.8222±0.0181</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.7731±0.0163</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.6251±0.0224</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.8231±0.0092</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.8294±0.0145</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.8374±0.0165</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.8402±0.0117</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.7989±0.0110</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.7865±0.0165</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.7368±0.0169</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.5511±0.0312</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.7827±0.0131</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.7697±0.0178</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.7212±0.0175</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.5406±0.0299</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.1020±0.0093</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0817±0.0116</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0533±0.0137</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0892±0.0199</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9428±0.0035</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9406±0.0044</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.9219±0.0053</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.8538±0.0106</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.8273±0.0118</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.8190±0.0159</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.7622±0.0157</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.6079±0.0222</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.8316±0.0130</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.8450±0.0144</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.8421±0.0134</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.8431±0.0182</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.8214±0.0116</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.8208±0.0141</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.7831±0.0135</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.6781±0.0165</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9272±0.0046</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.9242±0.0053</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.9004±0.0062</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.8199±0.0109</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.8054±0.0112</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.7982±0.0140</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.7456±0.0148</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.5967±0.0209</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.8303±0.0113</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.8276±0.0113</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.7899±0.0126</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.6755±0.0144</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.8158±0.0124</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.7973±0.0154</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.7244±0.0173</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.5516±0.0190</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.8493±0.0113</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.8644±0.0123</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.8738±0.0144</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.8827±0.0129</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.2568±0.0729</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.2186±0.0485</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.1479±0.0473</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.1708±0.0471</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.8246±0.0107</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.8217±0.0119</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.7811±0.0126</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.6646±0.0152</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.8085±0.0136</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.7895±0.0160</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.7105±0.0166</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.5349±0.0191</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.8414±0.0093</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.8568±0.0115</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.8675±0.0143</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.8782±0.0136</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.7748±0.0096</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.7494±0.0165</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.6549±0.0207</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.3811±0.0397</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.7575±0.0100</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.7308±0.0159</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.6360±0.0208</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.3682±0.0378</t>
         </is>
